--- a/data/merged/2026-10-08/MERGED_UK_Stick-Vacuum_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_UK_Stick-Vacuum_2026-10-08.xlsx
@@ -6473,13 +6473,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6996,50 +6996,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7365,7 +7321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -16252,40 +16208,40 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0F9YPP9C3</t>
+          <t>B09RMQ1XLL</t>
         </is>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>VYTRONIX</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0F9YPP9C3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Shark Disposable Hard Floor Vacuum and Mop Pad VACMOP Refill 16 Pack, WhitesWhite 1304HK200UK</t>
+          <t>VYTRONIX HSV3 Upright Vacuum CleanersLightweight 3-in-1 Compact Powerful Multifunction Corded Stick &amp; Handheld Vacuum | 600</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F9YPP9C3?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61y78uO9VYL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0F9YPP9C3</t>
+          <t>B09RMQ1XLL</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
@@ -16299,13 +16255,13 @@
         </is>
       </c>
       <c r="O39" s="15">
-        <v>1168</v>
+        <v>2191</v>
       </c>
       <c r="P39" s="15">
-        <v>65</v>
+        <v>1147</v>
       </c>
       <c r="Q39" s="16">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="R39" s="17" t="inlineStr">
         <is>
@@ -16314,89 +16270,101 @@
       </c>
       <c r="S39" s="18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T39" s="15">
-        <v>2056</v>
+        <v>921</v>
       </c>
       <c r="U39" s="16">
-        <v>-0.03</v>
+        <v>0.18</v>
       </c>
       <c r="V39" s="15">
-        <v>30819</v>
+        <v>30384</v>
       </c>
       <c r="W39" s="15" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="X39" s="15">
-        <v>29980</v>
+        <v>29691</v>
       </c>
       <c r="Y39" s="19">
         <v>1</v>
       </c>
       <c r="Z39" s="20">
-        <v>16.55</v>
+        <v>32.99</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="19">
-        <v>193</v>
+        <v>4176</v>
       </c>
       <c r="AE39" s="15">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AF39" s="21">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AG39" s="22">
-        <v>0.0034000000000000002</v>
+        <v>0.0163</v>
       </c>
       <c r="AH39" s="20">
-        <v>3.31</v>
+        <v>4.87</v>
       </c>
       <c r="AI39" s="16">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="13" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="AL39" s="19">
-        <v>498</v>
+        <v>1694</v>
       </c>
       <c r="AM39" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN39" s="13"/>
       <c r="AO39" s="13"/>
       <c r="AP39"/>
       <c r="AQ39" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR39" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AS39" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Vytronix</t>
         </is>
       </c>
       <c r="AT39" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU39" s="13"/>
-      <c r="AV39" s="14"/>
-      <c r="AW39" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU39" s="13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AV39" s="14" t="inlineStr">
+        <is>
+          <t>Dunstable Bedfordshire LU5 5UL GB</t>
+        </is>
+      </c>
+      <c r="AW39" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2</t>
+        </is>
+      </c>
       <c r="AX39" s="13"/>
       <c r="AY39" s="13" t="inlineStr">
         <is>
@@ -16411,11 +16379,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD39" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD39" s="13"/>
       <c r="BE39" s="13"/>
       <c r="BF39" s="13"/>
       <c r="BG39" s="13"/>
@@ -16427,47 +16391,47 @@
       </c>
       <c r="BJ39" s="23" t="inlineStr">
         <is>
-          <t>550 g</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BK39" s="23" t="inlineStr">
         <is>
-          <t>550.00 g</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL39" s="23" t="inlineStr">
         <is>
-          <t>9.9 x 15.5 x 25.4 cm</t>
+          <t>31 x 11 x 21 cm</t>
         </is>
       </c>
       <c r="BM39" s="23" t="inlineStr">
         <is>
-          <t>9.90 x 15.50 x 25.40 cm</t>
+          <t>31.00 x 11.00 x 21.00 cm</t>
         </is>
       </c>
       <c r="BN39" s="23" t="inlineStr">
         <is>
-          <t>550 g</t>
+          <t>2.71 kg</t>
         </is>
       </c>
       <c r="BO39" s="23" t="inlineStr">
         <is>
-          <t>550.00 g</t>
+          <t>2.71 kg</t>
         </is>
       </c>
       <c r="BP39" s="23" t="inlineStr">
         <is>
-          <t>26 x 16 x 16 cm</t>
+          <t>46 x 23.1 x 16.5 cm</t>
         </is>
       </c>
       <c r="BQ39" s="23" t="inlineStr">
         <is>
-          <t>26.00 x 16.00 x 16.00 cm</t>
+          <t>46.00 x 23.10 x 16.50 cm</t>
         </is>
       </c>
       <c r="BR39" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -16478,40 +16442,40 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B09RMQ1XLL</t>
+          <t>B0GVY4FWDK</t>
         </is>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>VYTRONIX</t>
+          <t>INTETURE</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/INTETURE/page/81A67A11-BDF9-40C2-8A10-6B3828AADF13?lp_asin=B0GVY4FWDK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>VYTRONIX HSV3 Upright Vacuum CleanersLightweight 3-in-1 Compact Powerful Multifunction Corded Stick &amp; Handheld Vacuum | 600</t>
+          <t>Cordless Vacuum Cleaner, 650W 55KPA Stick Vacuum with Touch Screen &amp; 3.3ft Flexible Hose, Up to 70 Mins Runtime, Self-Standin</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GVY4FWDK?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81amekLcGTL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B09RMQ1XLL</t>
+          <t>B0GVY4FWDK</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
@@ -16525,13 +16489,13 @@
         </is>
       </c>
       <c r="O40" s="15">
-        <v>2191</v>
+        <v>20856</v>
       </c>
       <c r="P40" s="15">
-        <v>1147</v>
+        <v>-341</v>
       </c>
       <c r="Q40" s="16">
-        <v>0.35</v>
+        <v>-0.02</v>
       </c>
       <c r="R40" s="17" t="inlineStr">
         <is>
@@ -16540,61 +16504,61 @@
       </c>
       <c r="S40" s="18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>49</t>
         </is>
       </c>
       <c r="T40" s="15">
-        <v>921</v>
+        <v>254</v>
       </c>
       <c r="U40" s="16">
-        <v>0.18</v>
+        <v>-0.13</v>
       </c>
       <c r="V40" s="15">
-        <v>30384</v>
+        <v>27937</v>
       </c>
       <c r="W40" s="15" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X40" s="15">
-        <v>29691</v>
+        <v>14077</v>
       </c>
       <c r="Y40" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z40" s="20">
-        <v>32.99</v>
+        <v>109.99</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="19">
-        <v>4176</v>
+        <v>1376</v>
       </c>
       <c r="AE40" s="15">
-        <v>15</v>
+        <v>645</v>
       </c>
       <c r="AF40" s="21">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AG40" s="22">
-        <v>0.0163</v>
+        <v>0</v>
       </c>
       <c r="AH40" s="20">
-        <v>4.87</v>
+        <v>3.71</v>
       </c>
       <c r="AI40" s="16">
-        <v>0.85</v>
+        <v>0.97</v>
       </c>
       <c r="AJ40"/>
       <c r="AK40" s="13" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AL40" s="19">
-        <v>1694</v>
+        <v>153</v>
       </c>
       <c r="AM40" s="13" t="inlineStr">
         <is>
@@ -16605,14 +16569,14 @@
       <c r="AO40" s="13"/>
       <c r="AP40"/>
       <c r="AQ40" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR40" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS40" s="14" t="inlineStr">
         <is>
-          <t>Vytronix</t>
+          <t>ROSIAL</t>
         </is>
       </c>
       <c r="AT40" s="13" t="inlineStr">
@@ -16622,25 +16586,21 @@
       </c>
       <c r="AU40" s="13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV40" s="14" t="inlineStr">
         <is>
-          <t>Dunstable Bedfordshire LU5 5UL GB</t>
+          <t>longgangqu guangdong 518000 CN</t>
         </is>
       </c>
       <c r="AW40" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3LXS32J3DCIBW</t>
         </is>
       </c>
       <c r="AX40" s="13"/>
-      <c r="AY40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY40" s="13"/>
       <c r="AZ40" s="13"/>
       <c r="BA40" s="13"/>
       <c r="BB40" s="13"/>
@@ -16649,59 +16609,59 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD40" s="13"/>
+      <c r="BD40" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE40" s="13"/>
       <c r="BF40" s="13"/>
       <c r="BG40" s="13"/>
       <c r="BH40" s="14"/>
-      <c r="BI40" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI40" s="23"/>
       <c r="BJ40" s="23" t="inlineStr">
         <is>
-          <t>2.5 kg</t>
+          <t>2.99 kg</t>
         </is>
       </c>
       <c r="BK40" s="23" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
+          <t>2.99 kg</t>
         </is>
       </c>
       <c r="BL40" s="23" t="inlineStr">
         <is>
-          <t>31 x 11 x 21 cm</t>
+          <t>20 x 20 x 30 cm</t>
         </is>
       </c>
       <c r="BM40" s="23" t="inlineStr">
         <is>
-          <t>31.00 x 11.00 x 21.00 cm</t>
+          <t>20.00 x 20.00 x 30.00 cm</t>
         </is>
       </c>
       <c r="BN40" s="23" t="inlineStr">
         <is>
-          <t>2.71 kg</t>
+          <t>4.49 kg</t>
         </is>
       </c>
       <c r="BO40" s="23" t="inlineStr">
         <is>
-          <t>2.71 kg</t>
+          <t>4.49 kg</t>
         </is>
       </c>
       <c r="BP40" s="23" t="inlineStr">
         <is>
-          <t>46 x 23.1 x 16.5 cm</t>
+          <t>44.4 x 33.5 x 19.6 cm</t>
         </is>
       </c>
       <c r="BQ40" s="23" t="inlineStr">
         <is>
-          <t>46.00 x 23.10 x 16.50 cm</t>
+          <t>44.40 x 33.50 x 19.60 cm</t>
         </is>
       </c>
       <c r="BR40" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -16712,40 +16672,40 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0GVY4FWDK</t>
+          <t>B0H6GD47Y5</t>
         </is>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>INTETURE</t>
+          <t>FAMIVAC</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/INTETURE/page/81A67A11-BDF9-40C2-8A10-6B3828AADF13?lp_asin=B0GVY4FWDK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/FAMIVAC/page/44653AEA-D58B-4928-84CE-E0C42E6865BA?lp_asin=B0H6GD47Y5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Cordless Vacuum Cleaner, 650W 55KPA Stick Vacuum with Touch Screen &amp; 3.3ft Flexible Hose, Up to 70 Mins Runtime, Self-Standin</t>
+          <t>FAMIVAC Cordless Vacuum Cleaner 70kPa/80Min Runtime with Charging StationsFoldable Wand,Anti-tangle Brush,LED Display,Dual</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GVY4FWDK?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H6GD47Y5?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81amekLcGTL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61jArs9smlL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0GVY4FWDK</t>
+          <t>B0H6GD47Y5</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -16759,13 +16719,13 @@
         </is>
       </c>
       <c r="O41" s="15">
-        <v>20856</v>
+        <v>3533</v>
       </c>
       <c r="P41" s="15">
-        <v>-341</v>
+        <v>101761</v>
       </c>
       <c r="Q41" s="16">
-        <v>-0.02</v>
+        <v>0.97</v>
       </c>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -16774,17 +16734,15 @@
       </c>
       <c r="S41" s="18" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T41" s="15">
-        <v>254</v>
-      </c>
-      <c r="U41" s="16">
-        <v>-0.13</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="U41" s="16"/>
       <c r="V41" s="15">
-        <v>27937</v>
+        <v>27509</v>
       </c>
       <c r="W41" s="15" t="inlineStr">
         <is>
@@ -16792,85 +16750,77 @@
         </is>
       </c>
       <c r="X41" s="15">
-        <v>14077</v>
+        <v>18774</v>
       </c>
       <c r="Y41" s="19">
         <v>2</v>
       </c>
       <c r="Z41" s="20">
-        <v>109.99</v>
+        <v>209.99</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="2"/>
       <c r="AD41" s="19">
-        <v>1376</v>
+        <v>31</v>
       </c>
       <c r="AE41" s="15">
-        <v>645</v>
+        <v>27</v>
       </c>
       <c r="AF41" s="21">
         <v>4.6</v>
       </c>
       <c r="AG41" s="22">
-        <v>0</v>
+        <v>0.2061</v>
       </c>
       <c r="AH41" s="20">
         <v>3.71</v>
       </c>
       <c r="AI41" s="16">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AL41" s="19">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="AM41" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN41" s="13"/>
       <c r="AO41" s="13"/>
       <c r="AP41"/>
       <c r="AQ41" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR41" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS41" s="14" t="inlineStr">
         <is>
-          <t>ROSIAL</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT41" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU41" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV41" s="14" t="inlineStr">
-        <is>
-          <t>longgangqu guangdong 518000 CN</t>
-        </is>
-      </c>
-      <c r="AW41" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3LXS32J3DCIBW</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU41" s="13"/>
+      <c r="AV41" s="14"/>
+      <c r="AW41" s="13"/>
       <c r="AX41" s="13"/>
-      <c r="AY41" s="13"/>
+      <c r="AY41" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ41" s="13"/>
       <c r="BA41" s="13"/>
       <c r="BB41" s="13"/>
@@ -16888,45 +16838,49 @@
       <c r="BF41" s="13"/>
       <c r="BG41" s="13"/>
       <c r="BH41" s="14"/>
-      <c r="BI41" s="23"/>
+      <c r="BI41" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ41" s="23" t="inlineStr">
         <is>
-          <t>2.99 kg</t>
+          <t>3 kg</t>
         </is>
       </c>
       <c r="BK41" s="23" t="inlineStr">
         <is>
-          <t>2.99 kg</t>
+          <t>3.00 kg</t>
         </is>
       </c>
       <c r="BL41" s="23" t="inlineStr">
         <is>
-          <t>20 x 20 x 30 cm</t>
+          <t>43.5 x 32.5 x 19 cm</t>
         </is>
       </c>
       <c r="BM41" s="23" t="inlineStr">
         <is>
-          <t>20.00 x 20.00 x 30.00 cm</t>
+          <t>43.50 x 32.50 x 19.00 cm</t>
         </is>
       </c>
       <c r="BN41" s="23" t="inlineStr">
         <is>
-          <t>4.49 kg</t>
+          <t>4.16 kg</t>
         </is>
       </c>
       <c r="BO41" s="23" t="inlineStr">
         <is>
-          <t>4.49 kg</t>
+          <t>4.16 kg</t>
         </is>
       </c>
       <c r="BP41" s="23" t="inlineStr">
         <is>
-          <t>44.4 x 33.5 x 19.6 cm</t>
+          <t>44 x 29.1 x 19.7 cm</t>
         </is>
       </c>
       <c r="BQ41" s="23" t="inlineStr">
         <is>
-          <t>44.40 x 33.50 x 19.60 cm</t>
+          <t>44.00 x 29.10 x 19.70 cm</t>
         </is>
       </c>
       <c r="BR41" s="13" t="inlineStr">
@@ -16942,40 +16896,40 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0H6GD47Y5</t>
+          <t>B0H2J8QH51</t>
         </is>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>FAMIVAC</t>
+          <t>VACTechPro</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/FAMIVAC/page/44653AEA-D58B-4928-84CE-E0C42E6865BA?lp_asin=B0H6GD47Y5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2J8QH51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>FAMIVAC Cordless Vacuum Cleaner 70kPa/80Min Runtime with Charging StationsFoldable Wand,Anti-tangle Brush,LED Display,Dual</t>
+          <t>VACTechPro F02 Lite Cordless Vacuum Cleaner, 40KPa/450W, Self-StandingsAnti-Tangle Stick Vacuum, Powerful &amp; Lightweight, An</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H6GD47Y5?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H2J8QH51?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61jArs9smlL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61RqesCLSIL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0H6GD47Y5</t>
+          <t>B0H2J8QH51</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -16989,13 +16943,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>3533</v>
+        <v>8718</v>
       </c>
       <c r="P42" s="15">
-        <v>101761</v>
+        <v>1637</v>
       </c>
       <c r="Q42" s="16">
-        <v>0.97</v>
+        <v>0.16</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -17004,63 +16958,65 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>131</v>
-      </c>
-      <c r="U42" s="16"/>
+        <v>341</v>
+      </c>
+      <c r="U42" s="16">
+        <v>11.13</v>
+      </c>
       <c r="V42" s="15">
-        <v>27509</v>
+        <v>25909</v>
       </c>
       <c r="W42" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>300</t>
         </is>
       </c>
       <c r="X42" s="15">
-        <v>18774</v>
+        <v>24063</v>
       </c>
       <c r="Y42" s="19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z42" s="20">
-        <v>209.99</v>
+        <v>75.98</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="19">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="AE42" s="15">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="AF42" s="21">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AG42" s="22">
-        <v>0.2061</v>
+        <v>0.0235</v>
       </c>
       <c r="AH42" s="20">
         <v>3.71</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN42" s="13"/>
@@ -17070,27 +17026,35 @@
         <v>10</v>
       </c>
       <c r="AR42" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>CHUANGJIN FAZHAN</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU42" s="13"/>
-      <c r="AV42" s="14"/>
-      <c r="AW42" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU42" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV42" s="14" t="inlineStr">
+        <is>
+          <t>300 LOCKHART ROAD WAN CHAI, 999077 HK</t>
+        </is>
+      </c>
+      <c r="AW42" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3O3PYUTF0LFO3</t>
+        </is>
+      </c>
       <c r="AX42" s="13"/>
-      <c r="AY42" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY42" s="13"/>
       <c r="AZ42" s="13"/>
       <c r="BA42" s="13"/>
       <c r="BB42" s="13"/>
@@ -17108,49 +17072,45 @@
       <c r="BF42" s="13"/>
       <c r="BG42" s="13"/>
       <c r="BH42" s="14"/>
-      <c r="BI42" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI42" s="23"/>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>3 kg</t>
+          <t>3.24 kg</t>
         </is>
       </c>
       <c r="BK42" s="23" t="inlineStr">
         <is>
-          <t>3.00 kg</t>
+          <t>3.24 kg</t>
         </is>
       </c>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>43.5 x 32.5 x 19 cm</t>
+          <t>35 x 15 x 22 cm</t>
         </is>
       </c>
       <c r="BM42" s="23" t="inlineStr">
         <is>
-          <t>43.50 x 32.50 x 19.00 cm</t>
+          <t>35.00 x 15.00 x 22.00 cm</t>
         </is>
       </c>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>4.16 kg</t>
+          <t>3.24 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>4.16 kg</t>
+          <t>3.24 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>44 x 29.1 x 19.7 cm</t>
+          <t>40.1 x 27.6 x 18.4 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>44.00 x 29.10 x 19.70 cm</t>
+          <t>40.10 x 27.60 x 18.40 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
@@ -17166,40 +17126,40 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0H2J8QH51</t>
+          <t>B0HGLVYWYL</t>
         </is>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>VACTechPro</t>
+          <t>SunSare</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2J8QH51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/SunSare/page/704CEB04-FAE8-4A8E-B261-EE8969E92DF7?lp_asin=B0HGLVYWYL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>VACTechPro F02 Lite Cordless Vacuum Cleaner, 40KPa/450W, Self-StandingsAnti-Tangle Stick Vacuum, Powerful &amp; Lightweight, An</t>
+          <t>Cordless Vacuum Cleaner, 650W 55KPa 70Mins Stick Vacuum with 90° Curved Adapter, 1m Hose, Aromatherapy, Wall-Mounted Charging</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H2J8QH51?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0HGLVYWYL?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61RqesCLSIL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41wpqZ7ozxL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0H2J8QH51</t>
+          <t>B0HGLVYWYL</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
@@ -17213,13 +17173,13 @@
         </is>
       </c>
       <c r="O43" s="15">
-        <v>8718</v>
+        <v>60152</v>
       </c>
       <c r="P43" s="15">
-        <v>1637</v>
+        <v>-39534</v>
       </c>
       <c r="Q43" s="16">
-        <v>0.16</v>
+        <v>-1.92</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
@@ -17228,61 +17188,59 @@
       </c>
       <c r="S43" s="18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>105</t>
         </is>
       </c>
       <c r="T43" s="15">
-        <v>341</v>
-      </c>
-      <c r="U43" s="16">
-        <v>11.13</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="U43" s="16"/>
       <c r="V43" s="15">
-        <v>25909</v>
+        <v>18143</v>
       </c>
       <c r="W43" s="15" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X43" s="15">
-        <v>24063</v>
+        <v>14955</v>
       </c>
       <c r="Y43" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z43" s="20">
-        <v>75.98</v>
+        <v>94.99</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="2"/>
       <c r="AD43" s="19">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="AE43" s="15">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="AF43" s="21">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AG43" s="22">
-        <v>0.0235</v>
+        <v>0.1466</v>
       </c>
       <c r="AH43" s="20">
         <v>3.71</v>
       </c>
       <c r="AI43" s="16">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
@@ -17293,14 +17251,14 @@
       <c r="AO43" s="13"/>
       <c r="AP43"/>
       <c r="AQ43" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR43" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
-          <t>CHUANGJIN FAZHAN</t>
+          <t>ZhouKuam</t>
         </is>
       </c>
       <c r="AT43" s="13" t="inlineStr">
@@ -17310,21 +17268,25 @@
       </c>
       <c r="AU43" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV43" s="14" t="inlineStr">
         <is>
-          <t>300 LOCKHART ROAD WAN CHAI, 999077 HK</t>
+          <t>深圳市 广东 518000 CN</t>
         </is>
       </c>
       <c r="AW43" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3O3PYUTF0LFO3</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2AEBBHMOT1XKA</t>
         </is>
       </c>
       <c r="AX43" s="13"/>
-      <c r="AY43" s="13"/>
+      <c r="AY43" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ43" s="13"/>
       <c r="BA43" s="13"/>
       <c r="BB43" s="13"/>
@@ -17342,45 +17304,45 @@
       <c r="BF43" s="13"/>
       <c r="BG43" s="13"/>
       <c r="BH43" s="14"/>
-      <c r="BI43" s="23"/>
+      <c r="BI43" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BK43" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL43" s="23" t="inlineStr">
         <is>
-          <t>35 x 15 x 22 cm</t>
-        </is>
-      </c>
-      <c r="BM43" s="23" t="inlineStr">
-        <is>
-          <t>35.00 x 15.00 x 22.00 cm</t>
-        </is>
-      </c>
+          <t>33L x 25W x 118H centimetres</t>
+        </is>
+      </c>
+      <c r="BM43" s="23"/>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>2.88 kg</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>2.88 kg</t>
         </is>
       </c>
       <c r="BP43" s="23" t="inlineStr">
         <is>
-          <t>40.1 x 27.6 x 18.4 cm</t>
+          <t>43.5 x 33 x 19.1 cm</t>
         </is>
       </c>
       <c r="BQ43" s="23" t="inlineStr">
         <is>
-          <t>40.10 x 27.60 x 18.40 cm</t>
+          <t>43.50 x 33.00 x 19.10 cm</t>
         </is>
       </c>
       <c r="BR43" s="13" t="inlineStr">
@@ -17396,40 +17358,40 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0HGLVYWYL</t>
+          <t>B0964H5ZSH</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>SunSare</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/SunSare/page/704CEB04-FAE8-4A8E-B261-EE8969E92DF7?lp_asin=B0HGLVYWYL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/BoschSmallDomesticAppliance/page/9EF251C5-8BF6-4E94-87AF-143928DFC8C7?lp_asin=B0964H5ZSH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Cordless Vacuum Cleaner, 650W 55KPa 70Mins Stick Vacuum with 90° Curved Adapter, 1m Hose, Aromatherapy, Wall-Mounted Charging</t>
+          <t>Bosch Series 2 Readyy'y Cordless Stick Vacuum Cleaner, BCHF216GB, Blues40 Minutes Runtime, 2in1 Functionality Handheld &amp; Va</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0HGLVYWYL?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0964H5ZSH?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41wpqZ7ozxL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61GaRzfCgsL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0HGLVYWYL</t>
+          <t>B0964H5ZSH</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -17443,13 +17405,13 @@
         </is>
       </c>
       <c r="O44" s="15">
-        <v>60152</v>
+        <v>10116</v>
       </c>
       <c r="P44" s="15">
-        <v>-39534</v>
+        <v>82319</v>
       </c>
       <c r="Q44" s="16">
-        <v>-1.92</v>
+        <v>0.9</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -17458,15 +17420,17 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>39</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>191</v>
-      </c>
-      <c r="U44" s="16"/>
+        <v>154</v>
+      </c>
+      <c r="U44" s="16">
+        <v>-0.51</v>
+      </c>
       <c r="V44" s="15">
-        <v>18143</v>
+        <v>14484</v>
       </c>
       <c r="W44" s="15" t="inlineStr">
         <is>
@@ -17474,83 +17438,73 @@
         </is>
       </c>
       <c r="X44" s="15">
-        <v>14955</v>
+        <v>16126</v>
       </c>
       <c r="Y44" s="19">
         <v>1</v>
       </c>
       <c r="Z44" s="20">
-        <v>94.99</v>
+        <v>109.32</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
-      <c r="AC44" s="2"/>
+      <c r="AC44" s="2">
+        <v>4</v>
+      </c>
       <c r="AD44" s="19">
-        <v>75</v>
+        <v>261</v>
       </c>
       <c r="AE44" s="15">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="AF44" s="21">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AG44" s="22">
-        <v>0.1466</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="AH44" s="20">
-        <v>3.71</v>
+        <v>5.28</v>
       </c>
       <c r="AI44" s="16">
-        <v>0.96</v>
+        <v>0.94</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>36</v>
+        <v>1948</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN44" s="13"/>
       <c r="AO44" s="13"/>
       <c r="AP44"/>
       <c r="AQ44" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR44" s="19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>ZhouKuam</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU44" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV44" s="14" t="inlineStr">
-        <is>
-          <t>深圳市 广东 518000 CN</t>
-        </is>
-      </c>
-      <c r="AW44" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2AEBBHMOT1XKA</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU44" s="13"/>
+      <c r="AV44" s="14"/>
+      <c r="AW44" s="13"/>
       <c r="AX44" s="13"/>
       <c r="AY44" s="13" t="inlineStr">
         <is>
@@ -17581,43 +17535,47 @@
       </c>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>2.5 kg</t>
+          <t>2.8 kg</t>
         </is>
       </c>
       <c r="BK44" s="23" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
+          <t>2.80 kg</t>
         </is>
       </c>
       <c r="BL44" s="23" t="inlineStr">
         <is>
-          <t>33L x 25W x 118H centimetres</t>
-        </is>
-      </c>
-      <c r="BM44" s="23"/>
+          <t>16.5 x 26.5 x 116 cm</t>
+        </is>
+      </c>
+      <c r="BM44" s="23" t="inlineStr">
+        <is>
+          <t>16.50 x 26.50 x 116.00 cm</t>
+        </is>
+      </c>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>2.88 kg</t>
+          <t>3.45 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>2.88 kg</t>
+          <t>3.45 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>43.5 x 33 x 19.1 cm</t>
+          <t>63.6 x 22.4 x 18 cm</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>43.50 x 33.00 x 19.10 cm</t>
+          <t>63.60 x 22.40 x 18.00 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -17628,40 +17586,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0964H5ZSH</t>
+          <t>B0GJTGBHBX</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>FAMIVAC</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/BoschSmallDomesticAppliance/page/9EF251C5-8BF6-4E94-87AF-143928DFC8C7?lp_asin=B0964H5ZSH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/FAMIVAC/page/44653AEA-D58B-4928-84CE-E0C42E6865BA?lp_asin=B0GJTGBHBX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Bosch Series 2 Readyy'y Cordless Stick Vacuum Cleaner, BCHF216GB, Blues40 Minutes Runtime, 2in1 Functionality Handheld &amp; Va</t>
+          <t>FAMIVAC FV3 Cordless Vacuum Cleaner,Powerful Stick Vacuum for Pet Hair Homes60KPa/50Min/120㎡,Foldable Tube,1.5KG Lightweigh</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0964H5ZSH?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GJTGBHBX?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61GaRzfCgsL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41WlhEFjBHL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0964H5ZSH</t>
+          <t>B0GJTGBHBX</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -17675,13 +17633,13 @@
         </is>
       </c>
       <c r="O45" s="15">
-        <v>10116</v>
+        <v>48526</v>
       </c>
       <c r="P45" s="15">
-        <v>82319</v>
+        <v>-16727</v>
       </c>
       <c r="Q45" s="16">
-        <v>0.9</v>
+        <v>-0.51</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -17690,63 +17648,55 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>93</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="U45" s="16">
-        <v>-0.51</v>
+        <v>-0.13</v>
       </c>
       <c r="V45" s="15">
-        <v>14484</v>
-      </c>
-      <c r="W45" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X45" s="15">
-        <v>16126</v>
-      </c>
+        <v>13856</v>
+      </c>
+      <c r="W45" s="15"/>
+      <c r="X45" s="15"/>
       <c r="Y45" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z45" s="20">
-        <v>109.32</v>
+        <v>88.82</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
-      <c r="AC45" s="2">
-        <v>4</v>
-      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" s="19">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AE45" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF45" s="21">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AG45" s="22">
-        <v>0.006500000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH45" s="20">
-        <v>5.28</v>
+        <v>3.71</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.94</v>
+        <v>0.96</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>1948</v>
+        <v>173</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
@@ -17760,7 +17710,7 @@
         <v>10</v>
       </c>
       <c r="AR45" s="19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
@@ -17774,13 +17724,13 @@
       </c>
       <c r="AU45" s="13"/>
       <c r="AV45" s="14"/>
-      <c r="AW45" s="13"/>
+      <c r="AW45" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2GKHWMJ2SPRFG</t>
+        </is>
+      </c>
       <c r="AX45" s="13"/>
-      <c r="AY45" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY45" s="13"/>
       <c r="AZ45" s="13"/>
       <c r="BA45" s="13"/>
       <c r="BB45" s="13"/>
@@ -17798,54 +17748,46 @@
       <c r="BF45" s="13"/>
       <c r="BG45" s="13"/>
       <c r="BH45" s="14"/>
-      <c r="BI45" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI45" s="23"/>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>2.8 kg</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BK45" s="23" t="inlineStr">
         <is>
-          <t>2.80 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>16.5 x 26.5 x 116 cm</t>
-        </is>
-      </c>
-      <c r="BM45" s="23" t="inlineStr">
-        <is>
-          <t>16.50 x 26.50 x 116.00 cm</t>
-        </is>
-      </c>
+          <t>43.5L x 32.5W x 19H centimetres</t>
+        </is>
+      </c>
+      <c r="BM45" s="23"/>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>3.45 kg</t>
+          <t>3.35 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>3.45 kg</t>
+          <t>3.35 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>63.6 x 22.4 x 18 cm</t>
+          <t>44.3 x 32.9 x 19 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>63.60 x 22.40 x 18.00 cm</t>
+          <t>44.30 x 32.90 x 19.00 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -17856,40 +17798,40 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0GJTGBHBX</t>
+          <t>B0C37SVX2V</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>FAMIVAC</t>
+          <t>Duronic</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/FAMIVAC/page/44653AEA-D58B-4928-84CE-E0C42E6865BA?lp_asin=B0GJTGBHBX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Duronic/page/A5A8FDD3-4203-4BE8-BCF2-850400F720CD?lp_asin=B0C37SVX2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>FAMIVAC FV3 Cordless Vacuum Cleaner,Powerful Stick Vacuum for Pet Hair Homes60KPa/50Min/120㎡,Foldable Tube,1.5KG Lightweigh</t>
+          <t>Duronic Cordless Vacuum Cleaner VC24 Rechargeable Upright Handheld Stick Cleaners, Bagless Powerful Hand Held Hoover for Floo</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GJTGBHBX?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0C37SVX2V?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41WlhEFjBHL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/910mk05nkrL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0GJTGBHBX</t>
+          <t>B0C37SVX2V</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -17903,13 +17845,13 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>48526</v>
+        <v>7867</v>
       </c>
       <c r="P46" s="15">
-        <v>-16727</v>
+        <v>20237</v>
       </c>
       <c r="Q46" s="16">
-        <v>-0.51</v>
+        <v>0.72</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -17918,89 +17860,109 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>156</v>
+        <v>306</v>
       </c>
       <c r="U46" s="16">
-        <v>-0.13</v>
+        <v>0.64</v>
       </c>
       <c r="V46" s="15">
-        <v>13856</v>
-      </c>
-      <c r="W46" s="15"/>
-      <c r="X46" s="15"/>
+        <v>12237</v>
+      </c>
+      <c r="W46" s="15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X46" s="15">
+        <v>4681</v>
+      </c>
       <c r="Y46" s="19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z46" s="20">
-        <v>88.82</v>
+        <v>66.24</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
-      <c r="AC46" s="2"/>
+      <c r="AC46" s="2">
+        <v>127</v>
+      </c>
       <c r="AD46" s="19">
-        <v>262</v>
+        <v>76</v>
       </c>
       <c r="AE46" s="15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF46" s="21">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AG46" s="22">
-        <v>0</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="AH46" s="20">
-        <v>3.71</v>
+        <v>5.28</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>173</v>
+        <v>1227</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN46" s="13"/>
       <c r="AO46" s="13"/>
       <c r="AP46"/>
       <c r="AQ46" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR46" s="19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>DURONIC</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU46" s="13"/>
-      <c r="AV46" s="14"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU46" s="13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AV46" s="14" t="inlineStr">
+        <is>
+          <t>ROMFORD Essex RM3 8SB GB</t>
+        </is>
+      </c>
       <c r="AW46" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2GKHWMJ2SPRFG</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=APLJ5AXPSKRV0</t>
         </is>
       </c>
       <c r="AX46" s="13"/>
-      <c r="AY46" s="13"/>
+      <c r="AY46" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
@@ -18018,46 +17980,54 @@
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
       <c r="BH46" s="14"/>
-      <c r="BI46" s="23"/>
+      <c r="BI46" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>2.5 kg</t>
+          <t>2.9 kg</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
+          <t>2.90 kg</t>
         </is>
       </c>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>43.5L x 32.5W x 19H centimetres</t>
-        </is>
-      </c>
-      <c r="BM46" s="23"/>
+          <t>25 x 34 x 93 cm</t>
+        </is>
+      </c>
+      <c r="BM46" s="23" t="inlineStr">
+        <is>
+          <t>25.00 x 34.00 x 93.00 cm</t>
+        </is>
+      </c>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>3.35 kg</t>
+          <t>3.38 kg</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>3.35 kg</t>
+          <t>3.38 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>44.3 x 32.9 x 19 cm</t>
+          <t>45.2 x 28.6 x 19.7 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>44.30 x 32.90 x 19.00 cm</t>
+          <t>45.20 x 28.60 x 19.70 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -18068,40 +18038,40 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0C37SVX2V</t>
+          <t>B0F8BBCT7W</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>Duronic</t>
+          <t>Tower</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Duronic/page/A5A8FDD3-4203-4BE8-BCF2-850400F720CD?lp_asin=B0C37SVX2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B0F8BBCT7W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Duronic Cordless Vacuum Cleaner VC24 Rechargeable Upright Handheld Stick Cleaners, Bagless Powerful Hand Held Hoover for Floo</t>
+          <t>Tower T513015 VL50 EVO FLEXI PET Pro Performance 3-in-1 Cordless Vacuum Cleaner with Cyclonic Suction, 1L Turbo Pet and Uphol</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0C37SVX2V?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0F8BBCT7W?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/910mk05nkrL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31ok0gcbq1L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0C37SVX2V</t>
+          <t>B0F8BBCT7W</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -18115,13 +18085,13 @@
         </is>
       </c>
       <c r="O47" s="15">
-        <v>7867</v>
+        <v>10148</v>
       </c>
       <c r="P47" s="15">
-        <v>20237</v>
+        <v>57057</v>
       </c>
       <c r="Q47" s="16">
-        <v>0.72</v>
+        <v>0.85</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
@@ -18130,103 +18100,83 @@
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>306</v>
+        <v>157</v>
       </c>
       <c r="U47" s="16">
-        <v>0.64</v>
+        <v>-0.05</v>
       </c>
       <c r="V47" s="15">
-        <v>12237</v>
-      </c>
-      <c r="W47" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X47" s="15">
-        <v>4681</v>
-      </c>
+        <v>11185</v>
+      </c>
+      <c r="W47" s="15"/>
+      <c r="X47" s="15"/>
       <c r="Y47" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z47" s="20">
-        <v>66.24</v>
+        <v>71.24</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
-      <c r="AC47" s="2">
-        <v>127</v>
-      </c>
+      <c r="AC47" s="2"/>
       <c r="AD47" s="19">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="AE47" s="15">
         <v>2</v>
       </c>
       <c r="AF47" s="21">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AG47" s="22">
-        <v>0.006500000000000001</v>
+        <v>0.0127</v>
       </c>
       <c r="AH47" s="20">
-        <v>5.28</v>
+        <v>3.71</v>
       </c>
       <c r="AI47" s="16">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>1227</v>
+        <v>513</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN47" s="13"/>
       <c r="AO47" s="13"/>
       <c r="AP47"/>
       <c r="AQ47" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR47" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>DURONIC</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU47" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV47" s="14" t="inlineStr">
-        <is>
-          <t>ROMFORD Essex RM3 8SB GB</t>
-        </is>
-      </c>
-      <c r="AW47" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=APLJ5AXPSKRV0</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU47" s="13"/>
+      <c r="AV47" s="14"/>
+      <c r="AW47" s="13"/>
       <c r="AX47" s="13"/>
       <c r="AY47" s="13" t="inlineStr">
         <is>
@@ -18257,47 +18207,43 @@
       </c>
       <c r="BJ47" s="23" t="inlineStr">
         <is>
-          <t>2.9 kg</t>
+          <t>2.3 Kilograms</t>
         </is>
       </c>
       <c r="BK47" s="23" t="inlineStr">
         <is>
-          <t>2.90 kg</t>
+          <t>2.30 kg</t>
         </is>
       </c>
       <c r="BL47" s="23" t="inlineStr">
         <is>
-          <t>25 x 34 x 93 cm</t>
-        </is>
-      </c>
-      <c r="BM47" s="23" t="inlineStr">
-        <is>
-          <t>25.00 x 34.00 x 93.00 cm</t>
-        </is>
-      </c>
+          <t>22L x 25W x 107H centimetres</t>
+        </is>
+      </c>
+      <c r="BM47" s="23"/>
       <c r="BN47" s="23" t="inlineStr">
         <is>
-          <t>3.38 kg</t>
+          <t>3.8 kg</t>
         </is>
       </c>
       <c r="BO47" s="23" t="inlineStr">
         <is>
-          <t>3.38 kg</t>
+          <t>3.80 kg</t>
         </is>
       </c>
       <c r="BP47" s="23" t="inlineStr">
         <is>
-          <t>45.2 x 28.6 x 19.7 cm</t>
+          <t>44.3 x 26.9 x 18.1 cm</t>
         </is>
       </c>
       <c r="BQ47" s="23" t="inlineStr">
         <is>
-          <t>45.20 x 28.60 x 19.70 cm</t>
+          <t>44.30 x 26.90 x 18.10 cm</t>
         </is>
       </c>
       <c r="BR47" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -18308,40 +18254,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0F8BBCT7W</t>
+          <t>B0DFWMTYX2</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Tower</t>
+          <t>VYTRONIX</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B0F8BBCT7W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B0DFWMTYX2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Tower T513015 VL50 EVO FLEXI PET Pro Performance 3-in-1 Cordless Vacuum Cleaner with Cyclonic Suction, 1L Turbo Pet and Uphol</t>
+          <t>VYTRONIX 3-in-1 Cordless Vacuum Cleaner – Lightweight Everyday Hoovers22.2V Battery | Up to 40 Min Runtime | Ideal for Flat</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F8BBCT7W?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DFWMTYX2?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31ok0gcbq1L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71eoz3JE8eL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0F8BBCT7W</t>
+          <t>B0DFWMTYX2</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -18355,13 +18301,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>10148</v>
+        <v>3087</v>
       </c>
       <c r="P48" s="15">
-        <v>57057</v>
+        <v>76716</v>
       </c>
       <c r="Q48" s="16">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -18370,89 +18316,103 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="U48" s="16">
-        <v>-0.05</v>
+        <v>6.75</v>
       </c>
       <c r="V48" s="15">
-        <v>11185</v>
-      </c>
-      <c r="W48" s="15"/>
-      <c r="X48" s="15"/>
+        <v>10853</v>
+      </c>
+      <c r="W48" s="15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X48" s="15">
+        <v>8232</v>
+      </c>
       <c r="Y48" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>71.24</v>
+        <v>64.99</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="19">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="AE48" s="15">
         <v>2</v>
       </c>
       <c r="AF48" s="21">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AG48" s="22">
-        <v>0.0127</v>
+        <v>0.012</v>
       </c>
       <c r="AH48" s="20">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="AI48" s="16">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>513</v>
+        <v>762</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
       <c r="AP48"/>
       <c r="AQ48" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR48" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Vytronix</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU48" s="13"/>
-      <c r="AV48" s="14"/>
-      <c r="AW48" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU48" s="13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AV48" s="14" t="inlineStr">
+        <is>
+          <t>Dunstable Bedfordshire LU5 5UL GB</t>
+        </is>
+      </c>
+      <c r="AW48" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2</t>
+        </is>
+      </c>
       <c r="AX48" s="13"/>
-      <c r="AY48" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY48" s="13"/>
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
       <c r="BB48" s="13"/>
@@ -18470,14 +18430,10 @@
       <c r="BF48" s="13"/>
       <c r="BG48" s="13"/>
       <c r="BH48" s="14"/>
-      <c r="BI48" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI48" s="23"/>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>2.3 Kilograms</t>
+          <t>2.3 kg</t>
         </is>
       </c>
       <c r="BK48" s="23" t="inlineStr">
@@ -18487,28 +18443,32 @@
       </c>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>22L x 25W x 107H centimetres</t>
-        </is>
-      </c>
-      <c r="BM48" s="23"/>
+          <t>22 x 23.5 x 110 cm</t>
+        </is>
+      </c>
+      <c r="BM48" s="23" t="inlineStr">
+        <is>
+          <t>22.00 x 23.50 x 110.00 cm</t>
+        </is>
+      </c>
       <c r="BN48" s="23" t="inlineStr">
         <is>
-          <t>3.8 kg</t>
+          <t>2.95 kg</t>
         </is>
       </c>
       <c r="BO48" s="23" t="inlineStr">
         <is>
-          <t>3.80 kg</t>
+          <t>2.95 kg</t>
         </is>
       </c>
       <c r="BP48" s="23" t="inlineStr">
         <is>
-          <t>44.3 x 26.9 x 18.1 cm</t>
+          <t>35.8 x 24.9 x 21.7 cm</t>
         </is>
       </c>
       <c r="BQ48" s="23" t="inlineStr">
         <is>
-          <t>44.30 x 26.90 x 18.10 cm</t>
+          <t>35.80 x 24.90 x 21.70 cm</t>
         </is>
       </c>
       <c r="BR48" s="13" t="inlineStr">
@@ -18524,40 +18484,40 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0DFWMTYX2</t>
+          <t>B07ZQH4T3T</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>VYTRONIX</t>
+          <t>JML</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B0DFWMTYX2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/JML/page/7D82F081-93D9-4B24-9DE9-D18ADF17C695?lp_asin=B07ZQH4T3T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>VYTRONIX 3-in-1 Cordless Vacuum Cleaner – Lightweight Everyday Hoovers22.2V Battery | Up to 40 Min Runtime | Ideal for Flat</t>
+          <t>JML Swivel Sweeper Cordless Vacuum Cleaner – Rechargeable Floor Sweepers360 degree swivel head bends under furniture – ligh</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DFWMTYX2?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B07ZQH4T3T?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71eoz3JE8eL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81IMjIncpDL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0DFWMTYX2</t>
+          <t>B07ZQH4T3T</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
@@ -18571,13 +18531,13 @@
         </is>
       </c>
       <c r="O49" s="15">
-        <v>3087</v>
+        <v>5798</v>
       </c>
       <c r="P49" s="15">
-        <v>76716</v>
+        <v>1389</v>
       </c>
       <c r="Q49" s="16">
-        <v>0.96</v>
+        <v>0.18</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
@@ -18586,84 +18546,86 @@
       </c>
       <c r="S49" s="18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T49" s="15">
-        <v>167</v>
+        <v>510</v>
       </c>
       <c r="U49" s="16">
-        <v>6.75</v>
+        <v>0.1</v>
       </c>
       <c r="V49" s="15">
-        <v>10853</v>
+        <v>7645</v>
       </c>
       <c r="W49" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>400</t>
         </is>
       </c>
       <c r="X49" s="15">
-        <v>8232</v>
+        <v>6864</v>
       </c>
       <c r="Y49" s="19">
         <v>1</v>
       </c>
       <c r="Z49" s="20">
-        <v>64.99</v>
+        <v>14.99</v>
       </c>
       <c r="AA49"/>
       <c r="AB49"/>
-      <c r="AC49" s="2"/>
+      <c r="AC49" s="2">
+        <v>21</v>
+      </c>
       <c r="AD49" s="19">
-        <v>9</v>
+        <v>2425</v>
       </c>
       <c r="AE49" s="15">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AF49" s="21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG49" s="22">
-        <v>0.012</v>
+        <v>0.0196</v>
       </c>
       <c r="AH49" s="20">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="AI49" s="16">
-        <v>0.94</v>
+        <v>0.77</v>
       </c>
       <c r="AJ49"/>
       <c r="AK49" s="13" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AL49" s="19">
-        <v>762</v>
+        <v>2184</v>
       </c>
       <c r="AM49" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49"/>
       <c r="AQ49" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR49" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS49" s="14" t="inlineStr">
         <is>
-          <t>Vytronix</t>
+          <t>JML Direct</t>
         </is>
       </c>
       <c r="AT49" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU49" s="13" t="inlineStr">
@@ -18673,16 +18635,20 @@
       </c>
       <c r="AV49" s="14" t="inlineStr">
         <is>
-          <t>Dunstable Bedfordshire LU5 5UL GB</t>
+          <t>London London W4 5RU GB</t>
         </is>
       </c>
       <c r="AW49" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KNWE4UE7YTH1</t>
         </is>
       </c>
       <c r="AX49" s="13"/>
-      <c r="AY49" s="13"/>
+      <c r="AY49" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ49" s="13"/>
       <c r="BA49" s="13"/>
       <c r="BB49" s="13"/>
@@ -18700,45 +18666,49 @@
       <c r="BF49" s="13"/>
       <c r="BG49" s="13"/>
       <c r="BH49" s="14"/>
-      <c r="BI49" s="23"/>
+      <c r="BI49" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ49" s="23" t="inlineStr">
         <is>
-          <t>2.3 kg</t>
+          <t>907 g</t>
         </is>
       </c>
       <c r="BK49" s="23" t="inlineStr">
         <is>
-          <t>2.30 kg</t>
+          <t>907.00 g</t>
         </is>
       </c>
       <c r="BL49" s="23" t="inlineStr">
         <is>
-          <t>22 x 23.5 x 110 cm</t>
+          <t>20 x 18 x 7 cm</t>
         </is>
       </c>
       <c r="BM49" s="23" t="inlineStr">
         <is>
-          <t>22.00 x 23.50 x 110.00 cm</t>
+          <t>20.00 x 18.00 x 7.00 cm</t>
         </is>
       </c>
       <c r="BN49" s="23" t="inlineStr">
         <is>
-          <t>2.95 kg</t>
+          <t>1.31 kg</t>
         </is>
       </c>
       <c r="BO49" s="23" t="inlineStr">
         <is>
-          <t>2.95 kg</t>
+          <t>1.31 kg</t>
         </is>
       </c>
       <c r="BP49" s="23" t="inlineStr">
         <is>
-          <t>35.8 x 24.9 x 21.7 cm</t>
+          <t>39.3 x 23.8 x 7.9 cm</t>
         </is>
       </c>
       <c r="BQ49" s="23" t="inlineStr">
         <is>
-          <t>35.80 x 24.90 x 21.70 cm</t>
+          <t>39.30 x 23.80 x 7.90 cm</t>
         </is>
       </c>
       <c r="BR49" s="13" t="inlineStr">
@@ -18754,40 +18724,40 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B07ZQH4T3T</t>
+          <t>B0H2L59XSD</t>
         </is>
       </c>
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>JML</t>
+          <t>Fieety</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/JML/page/7D82F081-93D9-4B24-9DE9-D18ADF17C695?lp_asin=B07ZQH4T3T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/Fieety/page/D431CF88-8046-4D96-9E7E-878D729FE6C3?lp_asin=B0H2L59XSD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>JML Swivel Sweeper Cordless Vacuum Cleaner – Rechargeable Floor Sweepers360 degree swivel head bends under furniture – ligh</t>
+          <t>130Mins 650W 55KPa Cordless Vacuum Cleaner with 2 Batteries Stick VacuumsTouchscreen Auto Mode Self-Standing &amp; Aroma, Wall-</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B07ZQH4T3T?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H2L59XSD?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81IMjIncpDL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61gf-RCggZL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B07ZQH4T3T</t>
+          <t>B0H2L59XSD</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
@@ -18801,13 +18771,13 @@
         </is>
       </c>
       <c r="O50" s="15">
-        <v>5798</v>
+        <v>19526</v>
       </c>
       <c r="P50" s="15">
-        <v>1389</v>
+        <v>840132</v>
       </c>
       <c r="Q50" s="16">
-        <v>0.18</v>
+        <v>0.98</v>
       </c>
       <c r="R50" s="17" t="inlineStr">
         <is>
@@ -18816,109 +18786,95 @@
       </c>
       <c r="S50" s="18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="T50" s="15">
-        <v>510</v>
-      </c>
-      <c r="U50" s="16">
-        <v>0.1</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="U50" s="16"/>
       <c r="V50" s="15">
-        <v>7645</v>
-      </c>
-      <c r="W50" s="15" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="X50" s="15">
-        <v>6864</v>
-      </c>
+        <v>5580</v>
+      </c>
+      <c r="W50" s="15"/>
+      <c r="X50" s="15"/>
       <c r="Y50" s="19">
         <v>1</v>
       </c>
       <c r="Z50" s="20">
-        <v>14.99</v>
+        <v>179.99</v>
       </c>
       <c r="AA50"/>
       <c r="AB50"/>
-      <c r="AC50" s="2">
-        <v>21</v>
-      </c>
+      <c r="AC50" s="2"/>
       <c r="AD50" s="19">
-        <v>2425</v>
+        <v>27</v>
       </c>
       <c r="AE50" s="15">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="AF50" s="21">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AG50" s="22">
-        <v>0.0196</v>
+        <v>0.8387</v>
       </c>
       <c r="AH50" s="20">
-        <v>3.4</v>
+        <v>3.71</v>
       </c>
       <c r="AI50" s="16">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="AJ50"/>
       <c r="AK50" s="13" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AL50" s="19">
-        <v>2184</v>
+        <v>73</v>
       </c>
       <c r="AM50" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN50" s="13"/>
       <c r="AO50" s="13"/>
       <c r="AP50"/>
       <c r="AQ50" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR50" s="19">
         <v>3</v>
       </c>
       <c r="AS50" s="14" t="inlineStr">
         <is>
-          <t>JML Direct</t>
+          <t>Zackyde</t>
         </is>
       </c>
       <c r="AT50" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU50" s="13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV50" s="14" t="inlineStr">
         <is>
-          <t>London London W4 5RU GB</t>
+          <t>深圳市 广东 518000 CN</t>
         </is>
       </c>
       <c r="AW50" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KNWE4UE7YTH1</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2FZTA3PZUI7OQ</t>
         </is>
       </c>
       <c r="AX50" s="13"/>
-      <c r="AY50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY50" s="13"/>
       <c r="AZ50" s="13"/>
       <c r="BA50" s="13"/>
       <c r="BB50" s="13"/>
@@ -18936,274 +18892,48 @@
       <c r="BF50" s="13"/>
       <c r="BG50" s="13"/>
       <c r="BH50" s="14"/>
-      <c r="BI50" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI50" s="23"/>
       <c r="BJ50" s="23" t="inlineStr">
         <is>
-          <t>907 g</t>
+          <t>3 kg</t>
         </is>
       </c>
       <c r="BK50" s="23" t="inlineStr">
         <is>
-          <t>907.00 g</t>
+          <t>3.00 kg</t>
         </is>
       </c>
       <c r="BL50" s="23" t="inlineStr">
         <is>
-          <t>20 x 18 x 7 cm</t>
+          <t>44 x 33 x 19 cm</t>
         </is>
       </c>
       <c r="BM50" s="23" t="inlineStr">
         <is>
-          <t>20.00 x 18.00 x 7.00 cm</t>
+          <t>44.00 x 33.00 x 19.00 cm</t>
         </is>
       </c>
       <c r="BN50" s="23" t="inlineStr">
         <is>
-          <t>1.31 kg</t>
+          <t>4.88 kg</t>
         </is>
       </c>
       <c r="BO50" s="23" t="inlineStr">
         <is>
-          <t>1.31 kg</t>
+          <t>4.88 kg</t>
         </is>
       </c>
       <c r="BP50" s="23" t="inlineStr">
         <is>
-          <t>39.3 x 23.8 x 7.9 cm</t>
+          <t>43.5 x 33 x 19.2 cm</t>
         </is>
       </c>
       <c r="BQ50" s="23" t="inlineStr">
         <is>
-          <t>39.30 x 23.80 x 7.90 cm</t>
+          <t>43.50 x 33.00 x 19.20 cm</t>
         </is>
       </c>
       <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0H2L59XSD</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>Fieety</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/stores/Fieety/page/D431CF88-8046-4D96-9E7E-878D729FE6C3?lp_asin=B0H2L59XSD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>130Mins 650W 55KPa Cordless Vacuum Cleaner with 2 Batteries Stick VacuumsTouchscreen Auto Mode Self-Standing &amp; Aroma, Wall-</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0H2L59XSD?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61gf-RCggZL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0H2L59XSD</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Stick Vacuums &amp; Electric Brooms</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>19526</v>
-      </c>
-      <c r="P51" s="15">
-        <v>840132</v>
-      </c>
-      <c r="Q51" s="16">
-        <v>0.98</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Stick Vacuums &amp; Electric Brooms</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="T51" s="15">
-        <v>31</v>
-      </c>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15">
-        <v>5580</v>
-      </c>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>179.99</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="19">
-        <v>27</v>
-      </c>
-      <c r="AE51" s="15">
-        <v>26</v>
-      </c>
-      <c r="AF51" s="21">
-        <v>4.8</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0.8387</v>
-      </c>
-      <c r="AH51" s="20">
-        <v>3.71</v>
-      </c>
-      <c r="AI51" s="16">
-        <v>0.98</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>73</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR51" s="19">
-        <v>3</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>Zackyde</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU51" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV51" s="14" t="inlineStr">
-        <is>
-          <t>深圳市 广东 518000 CN</t>
-        </is>
-      </c>
-      <c r="AW51" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2FZTA3PZUI7OQ</t>
-        </is>
-      </c>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>3 kg</t>
-        </is>
-      </c>
-      <c r="BK51" s="23" t="inlineStr">
-        <is>
-          <t>3.00 kg</t>
-        </is>
-      </c>
-      <c r="BL51" s="23" t="inlineStr">
-        <is>
-          <t>44 x 33 x 19 cm</t>
-        </is>
-      </c>
-      <c r="BM51" s="23" t="inlineStr">
-        <is>
-          <t>44.00 x 33.00 x 19.00 cm</t>
-        </is>
-      </c>
-      <c r="BN51" s="23" t="inlineStr">
-        <is>
-          <t>4.88 kg</t>
-        </is>
-      </c>
-      <c r="BO51" s="23" t="inlineStr">
-        <is>
-          <t>4.88 kg</t>
-        </is>
-      </c>
-      <c r="BP51" s="23" t="inlineStr">
-        <is>
-          <t>43.5 x 33 x 19.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ51" s="23" t="inlineStr">
-        <is>
-          <t>43.50 x 33.00 x 19.20 cm</t>
-        </is>
-      </c>
-      <c r="BR51" s="13" t="inlineStr">
         <is>
           <t>标准包裹</t>
         </is>
@@ -19488,108 +19218,101 @@
     <hyperlink ref="M38" r:id="rId273" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N38" r:id="rId274"/>
     <hyperlink ref="AW38" r:id="rId275" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3O3PYUTF0LFO3"/>
-    <hyperlink ref="C39" r:id="rId276" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3"/>
-    <hyperlink ref="G39" r:id="rId277" tooltip="https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0F9YPP9C3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J39" r:id="rId278" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3?psc=1"/>
-    <hyperlink ref="K39" r:id="rId279" tooltip="https://images-na.ssl-images-amazon.com/images/I/61y78uO9VYL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId280" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3"/>
+    <hyperlink ref="C39" r:id="rId276" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
+    <hyperlink ref="G39" r:id="rId277" tooltip="https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J39" r:id="rId278" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1"/>
+    <hyperlink ref="K39" r:id="rId279" tooltip="https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId280" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
     <hyperlink ref="M39" r:id="rId281" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N39" r:id="rId282"/>
-    <hyperlink ref="C40" r:id="rId283" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
-    <hyperlink ref="G40" r:id="rId284" tooltip="https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B09RMQ1XLL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J40" r:id="rId285" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL?psc=1"/>
-    <hyperlink ref="K40" r:id="rId286" tooltip="https://images-na.ssl-images-amazon.com/images/I/51QJB9vzthL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId287" tooltip="https://www.amazon.co.uk/dp/B09RMQ1XLL"/>
-    <hyperlink ref="M40" r:id="rId288" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N40" r:id="rId289"/>
-    <hyperlink ref="AW40" r:id="rId290" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2"/>
-    <hyperlink ref="C41" r:id="rId291" tooltip="https://www.amazon.co.uk/dp/B0GVY4FWDK"/>
-    <hyperlink ref="G41" r:id="rId292" tooltip="https://www.amazon.co.uk/stores/INTETURE/page/81A67A11-BDF9-40C2-8A10-6B3828AADF13?lp_asin=B0GVY4FWDK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J41" r:id="rId293" tooltip="https://www.amazon.co.uk/dp/B0GVY4FWDK?psc=1"/>
-    <hyperlink ref="K41" r:id="rId294" tooltip="https://images-na.ssl-images-amazon.com/images/I/81amekLcGTL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId295" tooltip="https://www.amazon.co.uk/dp/B0GVY4FWDK"/>
-    <hyperlink ref="M41" r:id="rId296" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N41" r:id="rId297"/>
-    <hyperlink ref="AW41" r:id="rId298" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3LXS32J3DCIBW"/>
-    <hyperlink ref="C42" r:id="rId299" tooltip="https://www.amazon.co.uk/dp/B0H6GD47Y5"/>
-    <hyperlink ref="G42" r:id="rId300" tooltip="https://www.amazon.co.uk/stores/FAMIVAC/page/44653AEA-D58B-4928-84CE-E0C42E6865BA?lp_asin=B0H6GD47Y5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J42" r:id="rId301" tooltip="https://www.amazon.co.uk/dp/B0H6GD47Y5?psc=1"/>
-    <hyperlink ref="K42" r:id="rId302" tooltip="https://images-na.ssl-images-amazon.com/images/I/61jArs9smlL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId303" tooltip="https://www.amazon.co.uk/dp/B0H6GD47Y5"/>
+    <hyperlink ref="AW39" r:id="rId283" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2"/>
+    <hyperlink ref="C40" r:id="rId284" tooltip="https://www.amazon.co.uk/dp/B0GVY4FWDK"/>
+    <hyperlink ref="G40" r:id="rId285" tooltip="https://www.amazon.co.uk/stores/INTETURE/page/81A67A11-BDF9-40C2-8A10-6B3828AADF13?lp_asin=B0GVY4FWDK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J40" r:id="rId286" tooltip="https://www.amazon.co.uk/dp/B0GVY4FWDK?psc=1"/>
+    <hyperlink ref="K40" r:id="rId287" tooltip="https://images-na.ssl-images-amazon.com/images/I/81amekLcGTL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId288" tooltip="https://www.amazon.co.uk/dp/B0GVY4FWDK"/>
+    <hyperlink ref="M40" r:id="rId289" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N40" r:id="rId290"/>
+    <hyperlink ref="AW40" r:id="rId291" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3LXS32J3DCIBW"/>
+    <hyperlink ref="C41" r:id="rId292" tooltip="https://www.amazon.co.uk/dp/B0H6GD47Y5"/>
+    <hyperlink ref="G41" r:id="rId293" tooltip="https://www.amazon.co.uk/stores/FAMIVAC/page/44653AEA-D58B-4928-84CE-E0C42E6865BA?lp_asin=B0H6GD47Y5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J41" r:id="rId294" tooltip="https://www.amazon.co.uk/dp/B0H6GD47Y5?psc=1"/>
+    <hyperlink ref="K41" r:id="rId295" tooltip="https://images-na.ssl-images-amazon.com/images/I/61jArs9smlL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId296" tooltip="https://www.amazon.co.uk/dp/B0H6GD47Y5"/>
+    <hyperlink ref="M41" r:id="rId297" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N41" r:id="rId298"/>
+    <hyperlink ref="C42" r:id="rId299" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51"/>
+    <hyperlink ref="G42" r:id="rId300" tooltip="https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2J8QH51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J42" r:id="rId301" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51?psc=1"/>
+    <hyperlink ref="K42" r:id="rId302" tooltip="https://images-na.ssl-images-amazon.com/images/I/61RqesCLSIL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId303" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51"/>
     <hyperlink ref="M42" r:id="rId304" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N42" r:id="rId305"/>
-    <hyperlink ref="C43" r:id="rId306" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51"/>
-    <hyperlink ref="G43" r:id="rId307" tooltip="https://www.amazon.co.uk/stores/VACTechPro/page/A2AA5919-757D-4EB7-AE3F-8644C68C4115?lp_asin=B0H2J8QH51&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J43" r:id="rId308" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51?psc=1"/>
-    <hyperlink ref="K43" r:id="rId309" tooltip="https://images-na.ssl-images-amazon.com/images/I/61RqesCLSIL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId310" tooltip="https://www.amazon.co.uk/dp/B0H2J8QH51"/>
-    <hyperlink ref="M43" r:id="rId311" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N43" r:id="rId312"/>
-    <hyperlink ref="AW43" r:id="rId313" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3O3PYUTF0LFO3"/>
-    <hyperlink ref="C44" r:id="rId314" tooltip="https://www.amazon.co.uk/dp/B0HGLVYWYL"/>
-    <hyperlink ref="G44" r:id="rId315" tooltip="https://www.amazon.co.uk/stores/SunSare/page/704CEB04-FAE8-4A8E-B261-EE8969E92DF7?lp_asin=B0HGLVYWYL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J44" r:id="rId316" tooltip="https://www.amazon.co.uk/dp/B0HGLVYWYL?psc=1"/>
-    <hyperlink ref="K44" r:id="rId317" tooltip="https://m.media-amazon.com/images/I/41wpqZ7ozxL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId318" tooltip="https://www.amazon.co.uk/dp/B0HGLVYWYL"/>
-    <hyperlink ref="M44" r:id="rId319" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N44" r:id="rId320"/>
-    <hyperlink ref="AW44" r:id="rId321" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2AEBBHMOT1XKA"/>
-    <hyperlink ref="C45" r:id="rId322" tooltip="https://www.amazon.co.uk/dp/B0964H5ZSH"/>
-    <hyperlink ref="G45" r:id="rId323" tooltip="https://www.amazon.co.uk/stores/BoschSmallDomesticAppliance/page/9EF251C5-8BF6-4E94-87AF-143928DFC8C7?lp_asin=B0964H5ZSH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J45" r:id="rId324" tooltip="https://www.amazon.co.uk/dp/B0964H5ZSH?psc=1"/>
-    <hyperlink ref="K45" r:id="rId325" tooltip="https://images-na.ssl-images-amazon.com/images/I/61GaRzfCgsL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId326" tooltip="https://www.amazon.co.uk/dp/B0964H5ZSH"/>
+    <hyperlink ref="AW42" r:id="rId306" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3O3PYUTF0LFO3"/>
+    <hyperlink ref="C43" r:id="rId307" tooltip="https://www.amazon.co.uk/dp/B0HGLVYWYL"/>
+    <hyperlink ref="G43" r:id="rId308" tooltip="https://www.amazon.co.uk/stores/SunSare/page/704CEB04-FAE8-4A8E-B261-EE8969E92DF7?lp_asin=B0HGLVYWYL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J43" r:id="rId309" tooltip="https://www.amazon.co.uk/dp/B0HGLVYWYL?psc=1"/>
+    <hyperlink ref="K43" r:id="rId310" tooltip="https://m.media-amazon.com/images/I/41wpqZ7ozxL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId311" tooltip="https://www.amazon.co.uk/dp/B0HGLVYWYL"/>
+    <hyperlink ref="M43" r:id="rId312" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N43" r:id="rId313"/>
+    <hyperlink ref="AW43" r:id="rId314" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2AEBBHMOT1XKA"/>
+    <hyperlink ref="C44" r:id="rId315" tooltip="https://www.amazon.co.uk/dp/B0964H5ZSH"/>
+    <hyperlink ref="G44" r:id="rId316" tooltip="https://www.amazon.co.uk/stores/BoschSmallDomesticAppliance/page/9EF251C5-8BF6-4E94-87AF-143928DFC8C7?lp_asin=B0964H5ZSH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J44" r:id="rId317" tooltip="https://www.amazon.co.uk/dp/B0964H5ZSH?psc=1"/>
+    <hyperlink ref="K44" r:id="rId318" tooltip="https://images-na.ssl-images-amazon.com/images/I/61GaRzfCgsL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId319" tooltip="https://www.amazon.co.uk/dp/B0964H5ZSH"/>
+    <hyperlink ref="M44" r:id="rId320" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N44" r:id="rId321"/>
+    <hyperlink ref="C45" r:id="rId322" tooltip="https://www.amazon.co.uk/dp/B0GJTGBHBX"/>
+    <hyperlink ref="G45" r:id="rId323" tooltip="https://www.amazon.co.uk/stores/FAMIVAC/page/44653AEA-D58B-4928-84CE-E0C42E6865BA?lp_asin=B0GJTGBHBX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J45" r:id="rId324" tooltip="https://www.amazon.co.uk/dp/B0GJTGBHBX?psc=1"/>
+    <hyperlink ref="K45" r:id="rId325" tooltip="https://m.media-amazon.com/images/I/41WlhEFjBHL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId326" tooltip="https://www.amazon.co.uk/dp/B0GJTGBHBX"/>
     <hyperlink ref="M45" r:id="rId327" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N45" r:id="rId328"/>
-    <hyperlink ref="C46" r:id="rId329" tooltip="https://www.amazon.co.uk/dp/B0GJTGBHBX"/>
-    <hyperlink ref="G46" r:id="rId330" tooltip="https://www.amazon.co.uk/stores/FAMIVAC/page/44653AEA-D58B-4928-84CE-E0C42E6865BA?lp_asin=B0GJTGBHBX&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J46" r:id="rId331" tooltip="https://www.amazon.co.uk/dp/B0GJTGBHBX?psc=1"/>
-    <hyperlink ref="K46" r:id="rId332" tooltip="https://m.media-amazon.com/images/I/41WlhEFjBHL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId333" tooltip="https://www.amazon.co.uk/dp/B0GJTGBHBX"/>
-    <hyperlink ref="M46" r:id="rId334" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N46" r:id="rId335"/>
-    <hyperlink ref="AW46" r:id="rId336" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2GKHWMJ2SPRFG"/>
-    <hyperlink ref="C47" r:id="rId337" tooltip="https://www.amazon.co.uk/dp/B0C37SVX2V"/>
-    <hyperlink ref="G47" r:id="rId338" tooltip="https://www.amazon.co.uk/stores/Duronic/page/A5A8FDD3-4203-4BE8-BCF2-850400F720CD?lp_asin=B0C37SVX2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J47" r:id="rId339" tooltip="https://www.amazon.co.uk/dp/B0C37SVX2V?psc=1"/>
-    <hyperlink ref="K47" r:id="rId340" tooltip="https://images-na.ssl-images-amazon.com/images/I/910mk05nkrL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId341" tooltip="https://www.amazon.co.uk/dp/B0C37SVX2V"/>
-    <hyperlink ref="M47" r:id="rId342" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N47" r:id="rId343"/>
-    <hyperlink ref="AW47" r:id="rId344" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=APLJ5AXPSKRV0"/>
-    <hyperlink ref="C48" r:id="rId345" tooltip="https://www.amazon.co.uk/dp/B0F8BBCT7W"/>
-    <hyperlink ref="G48" r:id="rId346" tooltip="https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B0F8BBCT7W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J48" r:id="rId347" tooltip="https://www.amazon.co.uk/dp/B0F8BBCT7W?psc=1"/>
-    <hyperlink ref="K48" r:id="rId348" tooltip="https://m.media-amazon.com/images/I/31ok0gcbq1L._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId349" tooltip="https://www.amazon.co.uk/dp/B0F8BBCT7W"/>
+    <hyperlink ref="AW45" r:id="rId329" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2GKHWMJ2SPRFG"/>
+    <hyperlink ref="C46" r:id="rId330" tooltip="https://www.amazon.co.uk/dp/B0C37SVX2V"/>
+    <hyperlink ref="G46" r:id="rId331" tooltip="https://www.amazon.co.uk/stores/Duronic/page/A5A8FDD3-4203-4BE8-BCF2-850400F720CD?lp_asin=B0C37SVX2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J46" r:id="rId332" tooltip="https://www.amazon.co.uk/dp/B0C37SVX2V?psc=1"/>
+    <hyperlink ref="K46" r:id="rId333" tooltip="https://images-na.ssl-images-amazon.com/images/I/910mk05nkrL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId334" tooltip="https://www.amazon.co.uk/dp/B0C37SVX2V"/>
+    <hyperlink ref="M46" r:id="rId335" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N46" r:id="rId336"/>
+    <hyperlink ref="AW46" r:id="rId337" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=APLJ5AXPSKRV0"/>
+    <hyperlink ref="C47" r:id="rId338" tooltip="https://www.amazon.co.uk/dp/B0F8BBCT7W"/>
+    <hyperlink ref="G47" r:id="rId339" tooltip="https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B0F8BBCT7W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J47" r:id="rId340" tooltip="https://www.amazon.co.uk/dp/B0F8BBCT7W?psc=1"/>
+    <hyperlink ref="K47" r:id="rId341" tooltip="https://m.media-amazon.com/images/I/31ok0gcbq1L._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId342" tooltip="https://www.amazon.co.uk/dp/B0F8BBCT7W"/>
+    <hyperlink ref="M47" r:id="rId343" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N47" r:id="rId344"/>
+    <hyperlink ref="C48" r:id="rId345" tooltip="https://www.amazon.co.uk/dp/B0DFWMTYX2"/>
+    <hyperlink ref="G48" r:id="rId346" tooltip="https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B0DFWMTYX2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J48" r:id="rId347" tooltip="https://www.amazon.co.uk/dp/B0DFWMTYX2?psc=1"/>
+    <hyperlink ref="K48" r:id="rId348" tooltip="https://images-na.ssl-images-amazon.com/images/I/71eoz3JE8eL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId349" tooltip="https://www.amazon.co.uk/dp/B0DFWMTYX2"/>
     <hyperlink ref="M48" r:id="rId350" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
     <hyperlink ref="N48" r:id="rId351"/>
-    <hyperlink ref="C49" r:id="rId352" tooltip="https://www.amazon.co.uk/dp/B0DFWMTYX2"/>
-    <hyperlink ref="G49" r:id="rId353" tooltip="https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B0DFWMTYX2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J49" r:id="rId354" tooltip="https://www.amazon.co.uk/dp/B0DFWMTYX2?psc=1"/>
-    <hyperlink ref="K49" r:id="rId355" tooltip="https://images-na.ssl-images-amazon.com/images/I/71eoz3JE8eL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId356" tooltip="https://www.amazon.co.uk/dp/B0DFWMTYX2"/>
-    <hyperlink ref="M49" r:id="rId357" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N49" r:id="rId358"/>
-    <hyperlink ref="AW49" r:id="rId359" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2"/>
-    <hyperlink ref="C50" r:id="rId360" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T"/>
-    <hyperlink ref="G50" r:id="rId361" tooltip="https://www.amazon.co.uk/stores/JML/page/7D82F081-93D9-4B24-9DE9-D18ADF17C695?lp_asin=B07ZQH4T3T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J50" r:id="rId362" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T?psc=1"/>
-    <hyperlink ref="K50" r:id="rId363" tooltip="https://images-na.ssl-images-amazon.com/images/I/81IMjIncpDL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId364" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T"/>
-    <hyperlink ref="M50" r:id="rId365" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N50" r:id="rId366"/>
-    <hyperlink ref="AW50" r:id="rId367" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KNWE4UE7YTH1"/>
-    <hyperlink ref="C51" r:id="rId368" tooltip="https://www.amazon.co.uk/dp/B0H2L59XSD"/>
-    <hyperlink ref="G51" r:id="rId369" tooltip="https://www.amazon.co.uk/stores/Fieety/page/D431CF88-8046-4D96-9E7E-878D729FE6C3?lp_asin=B0H2L59XSD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J51" r:id="rId370" tooltip="https://www.amazon.co.uk/dp/B0H2L59XSD?psc=1"/>
-    <hyperlink ref="K51" r:id="rId371" tooltip="https://images-na.ssl-images-amazon.com/images/I/61gf-RCggZL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId372" tooltip="https://www.amazon.co.uk/dp/B0H2L59XSD"/>
-    <hyperlink ref="M51" r:id="rId373" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
-    <hyperlink ref="N51" r:id="rId374"/>
-    <hyperlink ref="AW51" r:id="rId375" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2FZTA3PZUI7OQ"/>
+    <hyperlink ref="AW48" r:id="rId352" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2"/>
+    <hyperlink ref="C49" r:id="rId353" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T"/>
+    <hyperlink ref="G49" r:id="rId354" tooltip="https://www.amazon.co.uk/stores/JML/page/7D82F081-93D9-4B24-9DE9-D18ADF17C695?lp_asin=B07ZQH4T3T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J49" r:id="rId355" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T?psc=1"/>
+    <hyperlink ref="K49" r:id="rId356" tooltip="https://images-na.ssl-images-amazon.com/images/I/81IMjIncpDL._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId357" tooltip="https://www.amazon.co.uk/dp/B07ZQH4T3T"/>
+    <hyperlink ref="M49" r:id="rId358" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N49" r:id="rId359"/>
+    <hyperlink ref="AW49" r:id="rId360" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KNWE4UE7YTH1"/>
+    <hyperlink ref="C50" r:id="rId361" tooltip="https://www.amazon.co.uk/dp/B0H2L59XSD"/>
+    <hyperlink ref="G50" r:id="rId362" tooltip="https://www.amazon.co.uk/stores/Fieety/page/D431CF88-8046-4D96-9E7E-878D729FE6C3?lp_asin=B0H2L59XSD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J50" r:id="rId363" tooltip="https://www.amazon.co.uk/dp/B0H2L59XSD?psc=1"/>
+    <hyperlink ref="K50" r:id="rId364" tooltip="https://images-na.ssl-images-amazon.com/images/I/61gf-RCggZL._AC_US600_.jpg"/>
+    <hyperlink ref="L50" r:id="rId365" tooltip="https://www.amazon.co.uk/dp/B0H2L59XSD"/>
+    <hyperlink ref="M50" r:id="rId366" tooltip="https://www.amazon.co.uk/b?node=770072031"/>
+    <hyperlink ref="N50" r:id="rId367"/>
+    <hyperlink ref="AW50" r:id="rId368" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2FZTA3PZUI7OQ"/>
   </hyperlinks>
-  <drawing r:id="rId376"/>
+  <drawing r:id="rId369"/>
 </worksheet>
 </file>
 
@@ -19648,18 +19371,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>10275</v>
+        <v>8219</v>
       </c>
       <c r="C2" s="15">
-        <v>2290597</v>
+        <v>2259778</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>222.92914841849148</v>
+        <v>274.9456138216328</v>
       </c>
       <c r="G2" s="22">
-        <v>0.2177137408623795</v>
+        <v>0.18208201333658255</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19680,7 +19403,7 @@
         <v>258.3092583616093</v>
       </c>
       <c r="G3" s="22">
-        <v>0.04371225765441254</v>
+        <v>0.04570327211502249</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19701,7 +19424,7 @@
         <v>71.13887538486469</v>
       </c>
       <c r="G4" s="22">
-        <v>0.13075537662888018</v>
+        <v>0.1367110480958816</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19722,7 +19445,7 @@
         <v>389.19976218787156</v>
       </c>
       <c r="G5" s="22">
-        <v>0.017819684288589894</v>
+        <v>0.018631338753627682</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19743,7 +19466,7 @@
         <v>95.74196482716798</v>
       </c>
       <c r="G6" s="22">
-        <v>0.06988028392838225</v>
+        <v>0.07306320476749596</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19764,7 +19487,7 @@
         <v>101.98495989304813</v>
       </c>
       <c r="G7" s="22">
-        <v>0.06339654624430555</v>
+        <v>0.06628414453133653</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19785,7 +19508,7 @@
         <v>159.9903314917127</v>
       </c>
       <c r="G8" s="22">
-        <v>0.030681216230532896</v>
+        <v>0.03207869026783934</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19806,7 +19529,7 @@
         <v>141.03120464441218</v>
       </c>
       <c r="G9" s="22">
-        <v>0.029198008263587243</v>
+        <v>0.03052792485433882</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19827,7 +19550,7 @@
         <v>162.00538599640933</v>
       </c>
       <c r="G10" s="22">
-        <v>0.02360419535967793</v>
+        <v>0.024679323866279714</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19848,7 +19571,7 @@
         <v>58.22312099764071</v>
       </c>
       <c r="G11" s="22">
-        <v>0.06286682911325352</v>
+        <v>0.06573029974080064</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19869,7 +19592,7 @@
         <v>65.98987854251013</v>
       </c>
       <c r="G12" s="22">
-        <v>0.0523360525479394</v>
+        <v>0.05471986530494694</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19890,7 +19613,7 @@
         <v>99.98967297762478</v>
       </c>
       <c r="G13" s="22">
-        <v>0.02462125225129781</v>
+        <v>0.025742705864108643</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19911,7 +19634,7 @@
         <v>108.38819523269012</v>
       </c>
       <c r="G14" s="22">
-        <v>0.018667231698273123</v>
+        <v>0.019517490418485123</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19932,7 +19655,7 @@
         <v>179.9904397705545</v>
       </c>
       <c r="G15" s="22">
-        <v>0.011081682381608221</v>
+        <v>0.011586433018011032</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19953,7 +19676,7 @@
         <v>36.640729483282676</v>
       </c>
       <c r="G16" s="22">
-        <v>0.034855387223222796</v>
+        <v>0.03644298721726223</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19974,7 +19697,7 @@
         <v>64.5900755124056</v>
       </c>
       <c r="G17" s="22">
-        <v>0.019641911219408836</v>
+        <v>0.02053656483307118</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19995,7 +19718,7 @@
         <v>24.990073370738024</v>
       </c>
       <c r="G18" s="22">
-        <v>0.049094183705901046</v>
+        <v>0.051330335186867235</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20016,7 +19739,7 @@
         <v>143.0</v>
       </c>
       <c r="G19" s="22">
-        <v>0.008136455132959</v>
+        <v>0.008507055982631427</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20037,7 +19760,7 @@
         <v>67.98997134670488</v>
       </c>
       <c r="G20" s="22">
-        <v>0.014789702298972349</v>
+        <v>0.015463346551762335</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20058,7 +19781,7 @@
         <v>59.0</v>
       </c>
       <c r="G21" s="22">
-        <v>0.015722004449623902</v>
+        <v>0.016438113383105517</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20079,7 +19802,7 @@
         <v>144.12891986062718</v>
       </c>
       <c r="G22" s="22">
-        <v>0.006081152664477169</v>
+        <v>0.006358138195352135</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20100,7 +19823,7 @@
         <v>31.340016708437762</v>
       </c>
       <c r="G23" s="22">
-        <v>0.025362856234770633</v>
+        <v>0.026518088570858904</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20121,7 +19844,7 @@
         <v>109.98818897637796</v>
       </c>
       <c r="G24" s="22">
-        <v>0.005381926051488505</v>
+        <v>0.005627063071844746</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20142,7 +19865,7 @@
         <v>94.98952879581152</v>
       </c>
       <c r="G25" s="22">
-        <v>0.004047038881237419</v>
+        <v>0.004231374199694278</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20163,7 +19886,7 @@
         <v>94.05194805194805</v>
       </c>
       <c r="G26" s="22">
-        <v>0.003263057527280432</v>
+        <v>0.0034116839097011456</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20184,7 +19907,7 @@
         <v>39.990196078431374</v>
       </c>
       <c r="G27" s="22">
-        <v>0.006483737684076703</v>
+        <v>0.006779060236159418</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20205,7 +19928,7 @@
         <v>14.990196078431373</v>
       </c>
       <c r="G28" s="22">
-        <v>0.010806229473461172</v>
+        <v>0.011298433726932365</v>
       </c>
     </row>
   </sheetData>
@@ -20269,18 +19992,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>22556</v>
+        <v>20500</v>
       </c>
       <c r="C2" s="15">
-        <v>3447879</v>
+        <v>3417060</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>152.85861854938818</v>
+        <v>166.6858536585366</v>
       </c>
       <c r="G2" s="22">
-        <v>0.4779319843203729</v>
+        <v>0.4541527282394382</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20301,7 +20024,7 @@
         <v>399.99002347417843</v>
       </c>
       <c r="G3" s="22">
-        <v>0.03610551965250556</v>
+        <v>0.03775006092292696</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20322,7 +20045,7 @@
         <v>69.27599058454295</v>
       </c>
       <c r="G4" s="22">
-        <v>0.10801991736412755</v>
+        <v>0.11294002968608077</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20343,7 +20066,7 @@
         <v>159.9903314917127</v>
       </c>
       <c r="G5" s="22">
-        <v>0.030681216230532896</v>
+        <v>0.03207869026783934</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20364,7 +20087,7 @@
         <v>141.03120464441218</v>
       </c>
       <c r="G6" s="22">
-        <v>0.029198008263587243</v>
+        <v>0.03052792485433882</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20385,7 +20108,7 @@
         <v>162.00538599640933</v>
       </c>
       <c r="G7" s="22">
-        <v>0.02360419535967793</v>
+        <v>0.024679323866279714</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20406,7 +20129,7 @@
         <v>58.22312099764071</v>
       </c>
       <c r="G8" s="22">
-        <v>0.06286682911325352</v>
+        <v>0.06573029974080064</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20427,7 +20150,7 @@
         <v>65.98987854251013</v>
       </c>
       <c r="G9" s="22">
-        <v>0.0523360525479394</v>
+        <v>0.05471986530494694</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20448,7 +20171,7 @@
         <v>99.98967297762478</v>
       </c>
       <c r="G10" s="22">
-        <v>0.02462125225129781</v>
+        <v>0.025742705864108643</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20469,7 +20192,7 @@
         <v>179.9904397705545</v>
       </c>
       <c r="G11" s="22">
-        <v>0.011081682381608221</v>
+        <v>0.011586433018011032</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20490,7 +20213,7 @@
         <v>79.98974836905872</v>
       </c>
       <c r="G12" s="22">
-        <v>0.022735459264752622</v>
+        <v>0.023771018409800837</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20511,7 +20234,7 @@
         <v>64.5900755124056</v>
       </c>
       <c r="G13" s="22">
-        <v>0.019641911219408836</v>
+        <v>0.02053656483307118</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20532,7 +20255,7 @@
         <v>24.990073370738024</v>
       </c>
       <c r="G14" s="22">
-        <v>0.049094183705901046</v>
+        <v>0.051330335186867235</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20553,7 +20276,7 @@
         <v>31.340016708437762</v>
       </c>
       <c r="G15" s="22">
-        <v>0.025362856234770633</v>
+        <v>0.026518088570858904</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20574,7 +20297,7 @@
         <v>109.98818897637796</v>
       </c>
       <c r="G16" s="22">
-        <v>0.005381926051488505</v>
+        <v>0.005627063071844746</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20595,7 +20318,7 @@
         <v>94.98952879581152</v>
       </c>
       <c r="G17" s="22">
-        <v>0.004047038881237419</v>
+        <v>0.004231374199694278</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20616,7 +20339,7 @@
         <v>39.990196078431374</v>
       </c>
       <c r="G18" s="22">
-        <v>0.006483737684076703</v>
+        <v>0.006779060236159418</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20637,7 +20360,7 @@
         <v>14.990196078431373</v>
       </c>
       <c r="G19" s="22">
-        <v>0.010806229473461172</v>
+        <v>0.011298433726932365</v>
       </c>
     </row>
   </sheetData>
